--- a/dashboard/presales_status.xlsx
+++ b/dashboard/presales_status.xlsx
@@ -543,7 +543,7 @@
         <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>35.4</v>
+        <v>33.8</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -562,12 +562,12 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:31</t>
+          <t>2026-03-25 08:36:57</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:33</t>
+          <t>2026-03-25 08:37:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -618,12 +618,12 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:47</t>
+          <t>2026-03-25 08:38:13</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:51</t>
+          <t>2026-03-25 08:38:17</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -674,12 +674,12 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:58</t>
+          <t>2026-03-25 08:42:29</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:01</t>
+          <t>2026-03-25 08:42:32</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -730,12 +730,12 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:03</t>
+          <t>2026-03-25 08:42:34</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:06</t>
+          <t>2026-03-25 08:42:37</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -767,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -786,12 +786,12 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:42</t>
+          <t>2026-03-25 08:39:04</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:46</t>
+          <t>2026-03-25 08:39:07</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -842,12 +842,12 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:11</t>
+          <t>2026-03-25 08:42:43</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:13</t>
+          <t>2026-03-25 08:42:46</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -870,16 +870,16 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
         <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -898,12 +898,12 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:32</t>
+          <t>2026-03-25 08:37:57</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:34</t>
+          <t>2026-03-25 08:38:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -926,16 +926,16 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>48.9</v>
+        <v>48.2</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
@@ -954,12 +954,12 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:30</t>
+          <t>2026-03-25 08:37:55</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:32</t>
+          <t>2026-03-25 08:37:57</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -967,7 +967,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud - Monitoring Services [PRD0.L.178][PV0.8][DV1.0]</t>
+          <t>SD - Cegeka Security Advisory Framework - Active Directory Security Scan - PingCastle [PRD.4.1.004][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -985,13 +985,13 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>59.2</v>
+        <v>54</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1010,12 +1010,12 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:51</t>
+          <t>2026-03-25 08:41:08</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:54</t>
+          <t>2026-03-25 08:41:11</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SD - Generic - Hypervisor Management</t>
+          <t>SD - Cegeka Cloud - Monitoring Services [PRD0.L.178][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1047,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>58.6</v>
+        <v>59</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1066,12 +1066,12 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:21</t>
+          <t>2026-03-25 08:38:17</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:26</t>
+          <t>2026-03-25 08:38:22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SD - Generic - SAN &amp; Storage Device Management</t>
+          <t>SD - Generic - Hypervisor Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1103,7 +1103,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>57.6</v>
+        <v>58.6</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1122,12 +1122,12 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:30</t>
+          <t>2026-03-25 08:38:47</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:33</t>
+          <t>2026-03-25 08:38:50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SD - OS Management for IBM Power [PRD.0.L.128][PV0.8][DV1.0]</t>
+          <t>SD - Generic - SAN &amp; Storage Device Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1159,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>58.8</v>
+        <v>57.5</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1178,12 +1178,12 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:49</t>
+          <t>2026-03-25 08:38:53</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:53</t>
+          <t>2026-03-25 08:38:57</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1191,7 +1191,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SD - Cegeka Oracle Enterprise Manager [PRD.0.L.139][PV1.0][DV1.0]</t>
+          <t>SD - OS Management for IBM Power [PRD.0.L.128][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1206,26 +1206,26 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>39.3</v>
+        <v>58.7</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1234,12 +1234,12 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:10</t>
+          <t>2026-03-25 08:39:11</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:14</t>
+          <t>2026-03-25 08:39:14</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SD - Application Packaging &amp; Update Management [PRD.7.4.005][PV1.1][DV1.0]</t>
+          <t>SD - Cegeka Oracle Enterprise Manager [PRD.0.L.139][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,13 +1265,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1290,12 +1290,12 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:46</t>
+          <t>2026-03-25 08:37:36</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:49</t>
+          <t>2026-03-25 08:37:40</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SD - Automation as a Service [PRD.0.L.302][PV1.0][DV1.0]</t>
+          <t>SD - Application Packaging &amp; Update Management [PRD.7.4.005][PV1.1][DV1.0]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1321,13 +1321,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>41.3</v>
+        <v>39.5</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1346,12 +1346,12 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:34</t>
+          <t>2026-03-25 08:40:12</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:36</t>
+          <t>2026-03-25 08:40:16</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SD - Workspace Engine (Addendum) [PRD.7.7.001][PV1.0][DV1.0]</t>
+          <t>SD - Automation as a Service [PRD.0.L.302][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1377,13 +1377,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>57.2</v>
+        <v>41.3</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1402,12 +1402,12 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:07</t>
+          <t>2026-03-25 08:38:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:10</t>
+          <t>2026-03-25 08:38:02</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SD - Cegeka Security Advisory Framework - Active Directory Security Scan - PingCastle [PRD.4.1.004][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Security Advisory Framework - IGA Assessment - Elimity [PRD.4.1.004][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1430,16 +1430,16 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>58.5</v>
+        <v>53</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1458,12 +1458,12 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:40</t>
+          <t>2026-03-25 08:41:14</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:43</t>
+          <t>2026-03-25 08:41:17</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SD - IBM Power on Premise [DV0.9]</t>
+          <t>SD - Workspace Engine (Addendum) [PRD.7.7.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1486,13 +1486,13 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
         <v>57.3</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRODUCT_SUMMARY, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SCOPE, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1514,12 +1514,12 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:27</t>
+          <t>2026-03-25 08:40:34</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:31</t>
+          <t>2026-03-25 08:40:37</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud-Native Platform on Cegeka Cloud - Platform Engineering as a Service [PRD.0.5.001][PV2.2][DV1.0]</t>
+          <t>SD - IBM Power on Premise [DV0.9]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1542,26 +1542,26 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>39.7</v>
+        <v>57.2</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRODUCT_SUMMARY, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1570,12 +1570,12 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:48</t>
+          <t>2026-03-25 08:36:54</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:51</t>
+          <t>2026-03-25 08:36:57</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud-Native Platform on Cegeka Cloud [PRD.0.5.001][PV2.2][DV1.2]</t>
+          <t>SD - Cegeka Cloud-Native Platform on Cegeka Cloud - Platform Engineering as a Service [PRD.0.5.001][PV2.2][DV1.0]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1601,13 +1601,13 @@
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>44.5</v>
+        <v>39.7</v>
       </c>
       <c r="I21" t="n">
         <v>6</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1626,12 +1626,12 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:51</t>
+          <t>2026-03-25 08:37:15</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:55</t>
+          <t>2026-03-25 08:37:17</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SD - Cegeka OCI Managed Platform Services [PRD.0.4.001][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Cloud-Native Platform on Cegeka Cloud [PRD.0.5.001][PV2.2][DV1.2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1657,13 +1657,13 @@
         <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
       <c r="I22" t="n">
         <v>6</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1682,12 +1682,12 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-25 08:37:17</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:41</t>
+          <t>2026-03-25 08:37:22</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SD - Meeting Room [PRD.7.5.002][PV1.0][DV1.1]</t>
+          <t>SD - Cegeka OCI Managed Platform Services [PRD.0.4.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1713,13 +1713,13 @@
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H23" t="n">
-        <v>53.8</v>
+        <v>42.1</v>
       </c>
       <c r="I23" t="n">
         <v>6</v>
@@ -1729,21 +1729,21 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:56</t>
+          <t>2026-03-25 08:37:05</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:59</t>
+          <t>2026-03-25 08:37:08</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SD - Cegeka IBM Power Cloud(Legacy) [PRD.0.1.003][PV0.7][DV1.0]</t>
+          <t>SD - License Management - CSP License Rental [PRD.7.0.001][PV1.1][DV1.0]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1766,16 +1766,16 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>55.3</v>
+        <v>43.6</v>
       </c>
       <c r="I24" t="n">
         <v>6</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1794,12 +1794,12 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:21</t>
+          <t>2026-03-25 08:39:47</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:24</t>
+          <t>2026-03-25 08:39:50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SD - Cegeka Security Advisory Framework - IGA Assessment - Elimity [PRD.4.1.004][PV1.0][DV1.0]</t>
+          <t>SD - Meeting Room [PRD.7.5.002][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1822,16 +1822,16 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>57.3</v>
+        <v>53.4</v>
       </c>
       <c r="I25" t="n">
         <v>6</v>
@@ -1841,21 +1841,21 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:46</t>
+          <t>2026-03-25 08:40:24</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:48</t>
+          <t>2026-03-25 08:40:27</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SD - Generic - OS Management Windows</t>
+          <t>SD - Cegeka IBM Power Cloud(Legacy) [PRD.0.1.003][PV0.7][DV1.0]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1878,16 +1878,16 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>60.7</v>
+        <v>55.3</v>
       </c>
       <c r="I26" t="n">
         <v>6</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1906,12 +1906,12 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:26</t>
+          <t>2026-03-25 08:36:48</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:30</t>
+          <t>2026-03-25 08:36:51</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SD - Release and Deploy services for Argenta [PRD.0.L.191][PV0.7][DV1.0]</t>
+          <t>SD - Generic - OS Management Windows</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1934,16 +1934,16 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>59.8</v>
+        <v>60.7</v>
       </c>
       <c r="I27" t="n">
         <v>6</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1962,12 +1962,12 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:57</t>
+          <t>2026-03-25 08:38:50</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:01</t>
+          <t>2026-03-25 08:38:53</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud-Native Platform [PV2.0][DV1.2]</t>
+          <t>SD - Release and Deploy services for Argenta [PRD.0.L.191][PV0.7][DV1.0]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1990,16 +1990,16 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>60.8</v>
+        <v>58.9</v>
       </c>
       <c r="I28" t="n">
         <v>6</v>
@@ -2009,21 +2009,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:55</t>
+          <t>2026-03-25 08:39:18</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:01</t>
+          <t>2026-03-25 08:39:22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SD -  Managed Security Infrastructure [PRD.4.2.001][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Cloud-Native Platform [PV2.0][DV1.2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2046,26 +2046,26 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>45.7</v>
+        <v>59.8</v>
       </c>
       <c r="I29" t="n">
         <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -2074,12 +2074,12 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:50</t>
+          <t>2026-03-25 08:37:22</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:53</t>
+          <t>2026-03-25 08:37:27</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SD - Cegeka Azure Advisory Services - Microsoft Azure Cloud Solution Provider [PRD.0.2.002][PV1.0][DV1.0]</t>
+          <t>SD -  Managed Security Infrastructure [PRD.4.2.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>19</v>
       </c>
       <c r="H30" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
@@ -2121,21 +2121,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:33</t>
+          <t>2026-03-25 08:41:20</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:35</t>
+          <t>2026-03-25 08:41:22</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2143,7 +2143,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SD - Adoption &amp; Change Management - Purpose &amp; Culture [PRD.7.8.001][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Azure Advisory Services - Microsoft Azure Cloud Solution Provider [PRD.0.2.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2161,13 +2161,13 @@
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H31" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="I31" t="n">
         <v>6</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2186,12 +2186,12 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:20</t>
+          <t>2026-03-25 08:37:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:24</t>
+          <t>2026-03-25 08:37:02</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SD - Cegeka Managed File Transfer Services [PRD.0.6.002][PV1.0][DV1.0]</t>
+          <t>SD - Adoption &amp; Change Management - Purpose &amp; Culture [PRD.7.8.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2223,7 +2223,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>46.9</v>
+        <v>43.9</v>
       </c>
       <c r="I32" t="n">
         <v>6</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -2242,12 +2242,12 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:08</t>
+          <t>2026-03-25 08:40:48</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:10</t>
+          <t>2026-03-25 08:40:52</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SD - License Management - CSP License Rental [PRD.7.0.001][PV1.1][DV1.0]</t>
+          <t>SD - Adoption &amp; Change Management - Skilling &amp; Growth [PRD.7.8.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2273,23 +2273,23 @@
         <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="n">
-        <v>49.3</v>
+        <v>44.7</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>25</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2298,12 +2298,12 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:23</t>
+          <t>2026-03-25 08:40:52</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:26</t>
+          <t>2026-03-25 08:40:55</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SD - Onsite Support [PRD.7.6.002][PV1.0][DV1.1]</t>
+          <t>SD - Cegeka Managed File Transfer Services [PRD.0.6.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2329,13 +2329,13 @@
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H34" t="n">
-        <v>49.5</v>
+        <v>46.8</v>
       </c>
       <c r="I34" t="n">
         <v>6</v>
@@ -2354,12 +2354,12 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:35</t>
+          <t>2026-03-25 08:37:33</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:40</t>
+          <t>2026-03-25 08:37:36</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -2367,7 +2367,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SD - Cegeka Managed SD-WAN - powered by Cisco Meraki [PRD.4.5.002][PV1.0][DV1.2]</t>
+          <t>SD - Azure Managed Platform Services [PRD.0.2.020][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2382,26 +2382,26 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" t="n">
-        <v>51.4</v>
+        <v>49.3</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>25</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_NEEDS, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2410,12 +2410,12 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:55</t>
+          <t>2026-03-25 08:37:02</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:58</t>
+          <t>2026-03-25 08:37:05</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SD - Workspace Engine [PRD.7.7.001][PV1.0][DV1.0]</t>
+          <t>SD - Onsite Support [PRD.7.6.002][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2441,13 +2441,13 @@
         <v>12</v>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H36" t="n">
-        <v>57.4</v>
+        <v>48.4</v>
       </c>
       <c r="I36" t="n">
         <v>6</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2466,12 +2466,12 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:10</t>
+          <t>2026-03-25 08:41:03</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:13</t>
+          <t>2026-03-25 08:41:08</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SD - Dedicated LAN platform management [PRD.4.5.003][PV0.8][DV1.1]</t>
+          <t>SD - Workspace Engine [PRD.7.7.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>57.5</v>
+        <v>56.4</v>
       </c>
       <c r="I37" t="n">
         <v>6</v>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2522,12 +2522,12 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:01</t>
+          <t>2026-03-25 08:40:37</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:03</t>
+          <t>2026-03-25 08:40:40</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SD - Managed Application Delivery Controller F5 [PRD.4.5.006][PV0.8][DV1.0]</t>
+          <t>SD - Cegeka Security Advisory Framework - CISO Office as a Service [PRD.4.1.004][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2553,23 +2553,23 @@
         <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>59.4</v>
+        <v>55.9</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
         <v>25</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2578,12 +2578,12 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:06</t>
+          <t>2026-03-25 08:41:11</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:09</t>
+          <t>2026-03-25 08:41:14</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SD - Remote Support [PRD.7.6.001][PV1.0][DV1.2]</t>
+          <t>SD - Cegeka Security Advisory Framework - Third Party Risk Assessment - RiskRecon [PRD.4.1.004][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2609,13 +2609,13 @@
         <v>12</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>61</v>
+        <v>54.2</v>
       </c>
       <c r="I39" t="n">
         <v>6</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -2634,12 +2634,12 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:30</t>
+          <t>2026-03-25 08:41:17</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:35</t>
+          <t>2026-03-25 08:41:20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -2647,7 +2647,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Shared NAS Services [PRD.0.L.109][PV0.8][DV1.3]</t>
+          <t>SD - Dedicated LAN platform management [PRD.4.5.003][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2662,16 +2662,16 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>62.5</v>
+        <v>57</v>
       </c>
       <c r="I40" t="n">
         <v>6</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -2690,12 +2690,12 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:12</t>
+          <t>2026-03-25 08:42:32</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:16</t>
+          <t>2026-03-25 08:42:34</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - DFIR - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Managed Application Delivery Controller F5 [PRD.4.5.006][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2718,26 +2718,26 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>57.8</v>
+        <v>59.7</v>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
         <v>25</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, PRODUCT_SUMMARY, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -2746,12 +2746,12 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:06</t>
+          <t>2026-03-25 08:42:37</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:11</t>
+          <t>2026-03-25 08:42:40</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Compute IaaS Services [PRD.0.L.108][PV0.8][DV1.1]</t>
+          <t>SD - Cegeka Cloud Shared NAS Services [PRD.0.L.109][PV0.8][DV1.3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2777,23 +2777,23 @@
         <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>62.8</v>
+        <v>61.7</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>25</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -2802,12 +2802,12 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:54</t>
+          <t>2026-03-25 08:38:39</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:59</t>
+          <t>2026-03-25 08:38:43</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Shared LAN Services [PRD.0.L.102][PV0.8][DV1.1]</t>
+          <t>SD - Cegeka Modern SOC - DFIR - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2830,26 +2830,26 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>23</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>61.8</v>
+        <v>57.1</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
         <v>25</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, PRODUCT_SUMMARY, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2858,12 +2858,12 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:07</t>
+          <t>2026-03-25 08:41:35</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:12</t>
+          <t>2026-03-25 08:41:40</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SD - Dedicated Virtualization Environment Management [PRD.0.L.116][PV0.8][DV1.1]</t>
+          <t>SD - Cegeka Cloud Compute IaaS Services [PRD.0.L.108][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2895,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>61.4</v>
+        <v>62.9</v>
       </c>
       <c r="I44" t="n">
         <v>22</v>
@@ -2914,12 +2914,12 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:16</t>
+          <t>2026-03-25 08:38:22</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:21</t>
+          <t>2026-03-25 08:38:26</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SD - RedHat AMQ [PRD.0.L.136][PV0.8][DV1.0]</t>
+          <t>SD - Cegeka Cloud Shared LAN Services [PRD.0.L.102][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2942,16 +2942,16 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G45" t="n">
         <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="I45" t="n">
         <v>22</v>
@@ -2970,12 +2970,12 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:53</t>
+          <t>2026-03-25 08:38:35</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:57</t>
+          <t>2026-03-25 08:38:39</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SD - Takensysteem Application Management [PRD.0.L.188][PV0.7][DV1.0]</t>
+          <t>SD - Dedicated Virtualization Environment Management [PRD.0.L.116][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2998,16 +2998,16 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
         <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
       <c r="I46" t="n">
         <v>22</v>
@@ -3026,12 +3026,12 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:01</t>
+          <t>2026-03-25 08:38:43</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:05</t>
+          <t>2026-03-25 08:38:47</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SD - TAM IWS IBM Workload Scheduler [PRD.0.L.185][PV0.7][DV1.0]</t>
+          <t>SD - RedHat AMQ [PRD.0.L.136][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3063,7 +3063,7 @@
         <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="I47" t="n">
         <v>22</v>
@@ -3082,12 +3082,12 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:05</t>
+          <t>2026-03-25 08:39:14</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:09</t>
+          <t>2026-03-25 08:39:18</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -3095,7 +3095,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SD - TAM Oracle Goldengate [PRD.0.L.137][PV0.8][DV1.0]</t>
+          <t>SD - Takensysteem Application Management [PRD.0.L.188][PV0.7][DV1.0]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3110,16 +3110,16 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>62.4</v>
+        <v>61.6</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
@@ -3138,12 +3138,12 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:12</t>
+          <t>2026-03-25 08:39:22</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:16</t>
+          <t>2026-03-25 08:39:26</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SD - Technical Database management Microsoft SQL [PRD.0.L.129][PV0.8][DV1.1]</t>
+          <t>SD - TAM IWS IBM Workload Scheduler [PRD.0.L.185][PV0.7][DV1.0]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3175,7 +3175,7 @@
         <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>63.4</v>
+        <v>62.8</v>
       </c>
       <c r="I49" t="n">
         <v>22</v>
@@ -3194,12 +3194,12 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:16</t>
+          <t>2026-03-25 08:39:26</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:20</t>
+          <t>2026-03-25 08:39:31</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SD - Technical Database management Oracle [PRD.0.L.130][PV0.8][DV1.1]</t>
+          <t>SD - TAM Oracle Goldengate [PRD.0.L.137][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3231,7 +3231,7 @@
         <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>63.4</v>
+        <v>62.3</v>
       </c>
       <c r="I50" t="n">
         <v>22</v>
@@ -3250,12 +3250,12 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:20</t>
+          <t>2026-03-25 08:39:35</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:23</t>
+          <t>2026-03-25 08:39:39</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -3263,7 +3263,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SD - Adoption &amp; Change Management - Coaching &amp; Support [PRD.7.8.001][PV1.0][DV1.0]</t>
+          <t>SD - Technical Database management Microsoft SQL [PRD.0.L.129][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3278,26 +3278,26 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>44.5</v>
+        <v>63.5</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -3306,12 +3306,12 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:18</t>
+          <t>2026-03-25 08:39:39</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:20</t>
+          <t>2026-03-25 08:39:43</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SD - Power AIX (PAAS) [PRD.0.1.002][PV1.0][DV1.0]</t>
+          <t>SD - Technical Database management Oracle [PRD.0.L.130][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3334,26 +3334,26 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>46.2</v>
+        <v>63.6</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -3362,12 +3362,12 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:18</t>
+          <t>2026-03-25 08:39:43</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:21</t>
+          <t>2026-03-25 08:39:47</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SD - Power IBM i (PAAS) [PRD.0.1.004][PV1.0][DV1.0]</t>
+          <t>SD - Adoption &amp; Change Management - Coaching &amp; Support [PRD.7.8.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3393,23 +3393,23 @@
         <v>13</v>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>45.7</v>
+        <v>44.5</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>24</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -3418,12 +3418,12 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:24</t>
+          <t>2026-03-25 08:40:45</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:27</t>
+          <t>2026-03-25 08:40:48</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -3431,7 +3431,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SD - Adoption &amp; Change Management - Skilling &amp; Growth [PRD.7.8.001][PV1.0][DV1.0]</t>
+          <t>SD - Power AIX (PAAS) [PRD.0.1.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3449,23 +3449,23 @@
         <v>13</v>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" t="n">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -3474,12 +3474,12 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:24</t>
+          <t>2026-03-25 08:36:45</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:27</t>
+          <t>2026-03-25 08:36:48</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SD - Cegeka OS Management - Linux on Cegeka Cloud [PRD.0.L.126][PV1.0][DV1.0]</t>
+          <t>SD - Power IBM i (PAAS) [PRD.0.1.004][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3505,23 +3505,23 @@
         <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H55" t="n">
-        <v>49</v>
+        <v>45.6</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
         <v>24</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -3530,12 +3530,12 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:42</t>
+          <t>2026-03-25 08:36:51</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:44</t>
+          <t>2026-03-25 08:36:54</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SD - Cegeka OS Management - Linux on Microsoft Azure [PRD.0.L.126][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka OS Management - Linux on Cegeka Cloud [PRD.0.L.126][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3567,7 +3567,7 @@
         <v>16</v>
       </c>
       <c r="H56" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="I56" t="n">
         <v>6</v>
@@ -3586,12 +3586,12 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:44</t>
+          <t>2026-03-25 08:38:07</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:47</t>
+          <t>2026-03-25 08:38:10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SD - Cegeka OS Management - Windows on Cegeka Cloud [PRD.0.L.124][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka OS Management - Linux on Microsoft Azure [PRD.0.L.126][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3623,7 +3623,7 @@
         <v>16</v>
       </c>
       <c r="H57" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="I57" t="n">
         <v>6</v>
@@ -3642,12 +3642,12 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:36</t>
+          <t>2026-03-25 08:38:10</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:39</t>
+          <t>2026-03-25 08:38:13</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SD - Cegeka OS Management - Windows on Microsoft Azure [PRD.0.L.124][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka OS Management - Windows on Cegeka Cloud [PRD.0.L.124][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3679,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="H58" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="I58" t="n">
         <v>6</v>
@@ -3698,12 +3698,12 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:39</t>
+          <t>2026-03-25 08:38:02</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:42</t>
+          <t>2026-03-25 08:38:05</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -3711,7 +3711,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SD - Physical Workplace Management [PRD.7.4.001][PV1.1][DV1.0]</t>
+          <t>SD - Cegeka OS Management - Windows on Microsoft Azure [PRD.0.L.124][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3735,17 +3735,17 @@
         <v>16</v>
       </c>
       <c r="H59" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>24</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3754,12 +3754,12 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:39</t>
+          <t>2026-03-25 08:38:05</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:42</t>
+          <t>2026-03-25 08:38:07</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SD - Azure Managed Platform Services [PRD.0.2.020][PV2.0][DV1.0]</t>
+          <t>SD - Physical Workplace Management [PRD.7.4.001][PV1.1][DV1.0]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3785,23 +3785,23 @@
         <v>13</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H60" t="n">
-        <v>51.3</v>
+        <v>49.7</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
         <v>24</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -3810,12 +3810,12 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:35</t>
+          <t>2026-03-25 08:40:05</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-25 08:40:09</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -3847,7 +3847,7 @@
         <v>15</v>
       </c>
       <c r="H61" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="I61" t="n">
         <v>22</v>
@@ -3866,12 +3866,12 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:14</t>
+          <t>2026-03-25 08:37:40</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:17</t>
+          <t>2026-03-25 08:37:42</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SD - Cloud Data Backup &amp; Restore [PRD.7.1.003][PV1.0][DV1.1]</t>
+          <t>SD - Cegeka Managed SD-WAN - powered by Cisco Meraki [PRD.4.5.002][PV1.0][DV1.2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3897,23 +3897,23 @@
         <v>13</v>
       </c>
       <c r="F62" t="n">
+        <v>10</v>
+      </c>
+      <c r="G62" t="n">
         <v>14</v>
       </c>
-      <c r="G62" t="n">
-        <v>10</v>
-      </c>
       <c r="H62" t="n">
-        <v>55.8</v>
+        <v>51.1</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
         <v>24</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -3922,12 +3922,12 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:32</t>
+          <t>2026-03-25 08:42:26</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:35</t>
+          <t>2026-03-25 08:42:29</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -3935,7 +3935,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SD - Virtual Workplace Management [PRD.7.4.002][PV2.0][DV1.1]</t>
+          <t>SD - Cloud Data Backup &amp; Restore [PRD.7.1.003][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3953,23 +3953,23 @@
         <v>13</v>
       </c>
       <c r="F63" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H63" t="n">
-        <v>59.6</v>
+        <v>53.5</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>24</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3978,12 +3978,12 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:42</t>
+          <t>2026-03-25 08:39:57</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:46</t>
+          <t>2026-03-25 08:40:00</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -3991,7 +3991,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SD - Cegeka Security Advisory Framework - CISO Office as a Service [PRD.4.1.004][PV1.0][DV1.1]</t>
+          <t>SD - Virtual Workplace Management [PRD.7.4.002][PV2.0][DV1.1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4009,23 +4009,23 @@
         <v>13</v>
       </c>
       <c r="F64" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64" t="n">
-        <v>60.1</v>
+        <v>59.3</v>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
         <v>24</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ARCHITECTURAL_DESCRIPTION, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -4034,12 +4034,12 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:43</t>
+          <t>2026-03-25 08:40:09</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:46</t>
+          <t>2026-03-25 08:40:12</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4047,7 +4047,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SD - Cegeka Security Advisory Framework - Third Party Risk Assessment - RiskRecon [PRD.4.1.004][PV1.0][DV1.0]</t>
+          <t>SD - Digital Wellbeing [PRD.7.9.001][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4071,7 +4071,7 @@
         <v>6</v>
       </c>
       <c r="H65" t="n">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
       <c r="I65" t="n">
         <v>6</v>
@@ -4081,21 +4081,21 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:48</t>
+          <t>2026-03-25 08:40:55</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:50</t>
+          <t>2026-03-25 08:40:59</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SD - Device Lifecycle Management [PRD.7.3.001][PV1.0][DV1.1]</t>
+          <t>SD - Digital Workplace Security [PRD.7.1.001][PV1.0][DV2.0]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4127,7 +4127,7 @@
         <v>6</v>
       </c>
       <c r="H66" t="n">
-        <v>59.8</v>
+        <v>57.6</v>
       </c>
       <c r="I66" t="n">
         <v>6</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -4146,12 +4146,12 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:35</t>
+          <t>2026-03-25 08:39:50</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:39</t>
+          <t>2026-03-25 08:39:57</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SD - Digital Wellbeing [PRD.7.9.001][PV1.0][DV1.1]</t>
+          <t>SD - eXperience Management [PRD.7.2.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4174,16 +4174,16 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>58.7</v>
+        <v>59.9</v>
       </c>
       <c r="I67" t="n">
         <v>6</v>
@@ -4193,21 +4193,21 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:27</t>
+          <t>2026-03-25 08:40:30</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:30</t>
+          <t>2026-03-25 08:40:34</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -4215,7 +4215,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SD - Digital Workplace Security [PRD.7.1.001][PV1.0][DV2.0]</t>
+          <t>SD - Generic Service Catalogue</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4233,13 +4233,13 @@
         <v>13</v>
       </c>
       <c r="F68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
-        <v>60.2</v>
+        <v>60.3</v>
       </c>
       <c r="I68" t="n">
         <v>6</v>
@@ -4249,21 +4249,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:26</t>
+          <t>2026-03-25 08:38:57</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:32</t>
+          <t>2026-03-25 08:39:04</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -4271,7 +4271,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SD - Generic Service Catalogue</t>
+          <t>SD - Cegeka Modern SOC - Vectra - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4286,16 +4286,16 @@
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H69" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="I69" t="n">
         <v>6</v>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -4314,12 +4314,12 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:33</t>
+          <t>2026-03-25 08:42:14</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:42</t>
+          <t>2026-03-25 08:42:20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -4327,7 +4327,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Vectra - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Vectra - US [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4351,7 +4351,7 @@
         <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="I70" t="n">
         <v>6</v>
@@ -4370,12 +4370,12 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:45</t>
+          <t>2026-03-25 08:42:20</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:50</t>
+          <t>2026-03-25 08:42:26</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -4383,7 +4383,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Vectra - US [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Managed Dedicated FW platform [PRD.4.2.001][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4407,31 +4407,31 @@
         <v>4</v>
       </c>
       <c r="H71" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
         <v>24</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:50</t>
+          <t>2026-03-25 08:42:40</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:55</t>
+          <t>2026-03-25 08:42:43</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SD - Managed Dedicated FW platform [PRD.4.2.001][PV0.8][DV1.1]</t>
+          <t>SD - Cegeka Cloud Housing services [PRD.0.L.101][PV0.8][DV1.1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4457,13 +4457,13 @@
         <v>12</v>
       </c>
       <c r="F72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="I72" t="n">
         <v>22</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -4482,12 +4482,12 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:09</t>
+          <t>2026-03-25 08:38:26</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-03-24 16:46:11</t>
+          <t>2026-03-25 08:38:31</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Housing services [PRD.0.L.101][PV0.8][DV1.1]</t>
+          <t>SD - Cegeka Cloud Shared Backup Services [PRD.0.L.133][PV0.8][DV1.3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4510,16 +4510,16 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G73" t="n">
         <v>3</v>
       </c>
       <c r="H73" t="n">
-        <v>62.1</v>
+        <v>63.5</v>
       </c>
       <c r="I73" t="n">
         <v>22</v>
@@ -4538,12 +4538,12 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:59</t>
+          <t>2026-03-25 08:38:31</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:03</t>
+          <t>2026-03-25 08:38:35</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Shared Backup Services [PRD.0.L.133][PV0.8][DV1.3]</t>
+          <t>SD - Oracle Engineered System Management [PRD.0.L.202][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4575,7 +4575,7 @@
         <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>64.5</v>
+        <v>62.9</v>
       </c>
       <c r="I74" t="n">
         <v>22</v>
@@ -4594,12 +4594,12 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:03</t>
+          <t>2026-03-25 08:39:07</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:07</t>
+          <t>2026-03-25 08:39:11</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SD - Oracle Engineered System Management [PRD.0.L.202][PV0.8][DV1.0]</t>
+          <t>SD - TAM Oracle Data Integrator ODI [PRD.0.L.138][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>62.9</v>
+        <v>62.6</v>
       </c>
       <c r="I75" t="n">
         <v>22</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -4650,12 +4650,12 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:46</t>
+          <t>2026-03-25 08:39:31</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-03-24 16:42:49</t>
+          <t>2026-03-25 08:39:35</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SD - TAM Oracle Data Integrator ODI [PRD.0.L.138][PV0.8][DV1.0]</t>
+          <t>SD - Cegeka Cloud Housing Services [PRD.0.L.101][PV0.8][DV1.2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4678,16 +4678,16 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
       <c r="I76" t="n">
         <v>22</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -4706,12 +4706,12 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:09</t>
+          <t>2026-03-25 08:37:49</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:12</t>
+          <t>2026-03-25 08:37:52</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -4719,109 +4719,109 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SD - Cegeka Cloud Housing Services [PRD.0.L.101][PV0.8][DV1.2]</t>
+          <t>SD - APM Dynatrace (Application Performance Monitoring) [PRD.0.L.135][PV0.8][DV1.0]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PIPELINE COMPLETED</t>
+          <t>json_to_xml (internal)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>62.8</v>
+        <v>65.7</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J77" t="n">
         <v>24</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>2026-03-24 16:41:24</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>2026-03-24 16:41:27</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SD - APM Dynatrace (Application Performance Monitoring) [PRD.0.L.135][PV0.8][DV1.0]</t>
+          <t>SD - Cegeka Technical Application Management [PRD.0.6.001][PV1.2][DV1.1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>json_to_xml (internal)</t>
+          <t>PIPELINE COMPLETED</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F78" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H78" t="n">
-        <v>65.7</v>
+        <v>48.7</v>
       </c>
       <c r="I78" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-03-25 08:37:27</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-03-25 08:37:30</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SD - Cegeka Technical Application Management [PRD.0.6.001][PV1.2][DV1.1]</t>
+          <t>SD - TAM Services [PRD.0.6.001][PV1.1][DV1.1] - Word file</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4845,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="H79" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="I79" t="n">
         <v>6</v>
@@ -4864,12 +4864,12 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:01</t>
+          <t>2026-03-25 08:37:30</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:05</t>
+          <t>2026-03-25 08:37:33</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SD - TAM Services [PRD.0.6.001][PV1.1][DV1.1] - Word file</t>
+          <t>SD - Digital Identity Services [PRD.7.5.005][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4892,26 +4892,26 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G80" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H80" t="n">
-        <v>49.1</v>
+        <v>56</v>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
         <v>23</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TERMS_CONDITIONS, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4920,12 +4920,12 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:05</t>
+          <t>2026-03-25 08:40:27</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:08</t>
+          <t>2026-03-25 08:40:30</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SD - Digital Identity Services [PRD.7.5.005][PV1.0][DV1.1]</t>
+          <t>SD - Workplace Assistant [PRD.7.7.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4948,16 +4948,16 @@
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>57.9</v>
+        <v>59.4</v>
       </c>
       <c r="I81" t="n">
         <v>22</v>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4976,12 +4976,12 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:59</t>
+          <t>2026-03-25 08:40:40</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:02</t>
+          <t>2026-03-25 08:40:45</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SD - Workplace Assistant [PRD.7.7.002][PV1.0][DV1.0]</t>
+          <t>SD - Device Lifecycle Management [PRD.7.3.001][PV1.0][DV1.1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5007,23 +5007,23 @@
         <v>14</v>
       </c>
       <c r="F82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H82" t="n">
-        <v>58.7</v>
+        <v>60.1</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
         <v>23</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, REQUIREMENTS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -5032,12 +5032,12 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:13</t>
+          <t>2026-03-25 08:40:00</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:18</t>
+          <t>2026-03-25 08:40:05</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SD - Cegeka ExaCC Services [PRD.0.4.002][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - CrowdStrike - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5063,13 +5063,13 @@
         <v>13</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H83" t="n">
-        <v>60.7</v>
+        <v>61.9</v>
       </c>
       <c r="I83" t="n">
         <v>6</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -5088,12 +5088,12 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:41</t>
+          <t>2026-03-25 08:41:22</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:45</t>
+          <t>2026-03-25 08:41:29</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SD - Cegeka ExaCC Services [PRD.0.4.002][PV1.1][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - CrowdStrike - US [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5119,13 +5119,13 @@
         <v>13</v>
       </c>
       <c r="F84" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>60.3</v>
+        <v>61.9</v>
       </c>
       <c r="I84" t="n">
         <v>6</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OPERATIONAL_SUPPORT, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -5144,12 +5144,12 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:45</t>
+          <t>2026-03-25 08:41:29</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:48</t>
+          <t>2026-03-25 08:41:35</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - CrowdStrike - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Microsoft - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>4</v>
       </c>
       <c r="H85" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="I85" t="n">
         <v>6</v>
@@ -5200,12 +5200,12 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:53</t>
+          <t>2026-03-25 08:41:40</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:58</t>
+          <t>2026-03-25 08:41:46</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - CrowdStrike - US [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Microsoft - US [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5237,7 +5237,7 @@
         <v>4</v>
       </c>
       <c r="H86" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="I86" t="n">
         <v>6</v>
@@ -5256,12 +5256,12 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:58</t>
+          <t>2026-03-25 08:41:46</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:06</t>
+          <t>2026-03-25 08:41:52</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -5269,7 +5269,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Microsoft - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Recorded Future - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5293,7 +5293,7 @@
         <v>4</v>
       </c>
       <c r="H87" t="n">
-        <v>62.8</v>
+        <v>61</v>
       </c>
       <c r="I87" t="n">
         <v>6</v>
@@ -5307,17 +5307,17 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:11</t>
+          <t>2026-03-25 08:41:52</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:17</t>
+          <t>2026-03-25 08:41:58</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -5325,7 +5325,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Microsoft - US [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Recorded Future - US [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5349,7 +5349,7 @@
         <v>4</v>
       </c>
       <c r="H88" t="n">
-        <v>62.8</v>
+        <v>61</v>
       </c>
       <c r="I88" t="n">
         <v>6</v>
@@ -5363,17 +5363,17 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:17</t>
+          <t>2026-03-25 08:41:58</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:22</t>
+          <t>2026-03-25 08:42:02</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Recorded Future - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Sentinel One - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5405,7 +5405,7 @@
         <v>4</v>
       </c>
       <c r="H89" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
       <c r="I89" t="n">
         <v>6</v>
@@ -5419,17 +5419,17 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:22</t>
+          <t>2026-03-25 08:42:02</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:27</t>
+          <t>2026-03-25 08:42:08</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -5437,7 +5437,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Recorded Future - US [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Cegeka Modern SOC - Splunk - EU [PRD.4.3.008][PV1.0][DV1.8]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5461,7 +5461,7 @@
         <v>4</v>
       </c>
       <c r="H90" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="I90" t="n">
         <v>6</v>
@@ -5475,17 +5475,17 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:27</t>
+          <t>2026-03-25 08:42:08</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:33</t>
+          <t>2026-03-25 08:42:14</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Sentinel One - EU [PRD.4.3.008][PV2.0][DV1.0]</t>
+          <t>SD - Remote Support [PRD.7.6.001][PV1.0][DV1.2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5508,40 +5508,40 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G91" t="n">
         <v>4</v>
       </c>
       <c r="H91" t="n">
-        <v>61.9</v>
+        <v>63.5</v>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J91" t="n">
         <v>23</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:33</t>
+          <t>2026-03-25 08:40:59</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:39</t>
+          <t>2026-03-25 08:41:03</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -5549,7 +5549,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SD - Cegeka Modern SOC - Splunk - EU [PRD.4.3.008][PV1.0][DV1.8]</t>
+          <t>SD - Teamwork [PRD.7.5.001][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5573,7 +5573,7 @@
         <v>4</v>
       </c>
       <c r="H92" t="n">
-        <v>61.9</v>
+        <v>58.8</v>
       </c>
       <c r="I92" t="n">
         <v>6</v>
@@ -5583,21 +5583,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, PRICING_ELEMENTS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:39</t>
+          <t>2026-03-25 08:40:20</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-03-24 16:45:45</t>
+          <t>2026-03-25 08:40:24</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -5605,7 +5605,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SD - eXperience Management [PRD.7.2.001][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka Housing Services [PRD.0.L.101][PV0.8][DV1.3]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5620,16 +5620,16 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>61.8</v>
+        <v>63.1</v>
       </c>
       <c r="I93" t="n">
         <v>22</v>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -5648,12 +5648,12 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:03</t>
+          <t>2026-03-25 08:37:52</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-03-24 16:44:07</t>
+          <t>2026-03-25 08:37:55</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SD - Teamwork [PRD.7.5.001][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka DBMS for Oracle on IaaS [PRD.0.9.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5676,26 +5676,26 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F94" t="n">
         <v>13</v>
       </c>
-      <c r="F94" t="n">
-        <v>20</v>
-      </c>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H94" t="n">
-        <v>61.9</v>
+        <v>58.9</v>
       </c>
       <c r="I94" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -5704,12 +5704,12 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:53</t>
+          <t>2026-03-25 08:37:46</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:56</t>
+          <t>2026-03-25 08:37:49</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -5717,7 +5717,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SD - Cegeka Housing Services [PRD.0.L.101][PV0.8][DV1.3]</t>
+          <t>SD - Cegeka ExaCC Services [PRD.0.4.002][PV1.0][DV1.0]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5732,40 +5732,40 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>63.1</v>
+        <v>61.8</v>
       </c>
       <c r="I95" t="n">
+        <v>6</v>
+      </c>
+      <c r="J95" t="n">
         <v>22</v>
       </c>
-      <c r="J95" t="n">
-        <v>23</v>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, DIFFERENTIATORS, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_PROJECT_DESC, TRANSITION_TRANSFORMATION, VALUE_PROPOSITION</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:27</t>
+          <t>2026-03-25 08:37:08</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:30</t>
+          <t>2026-03-25 08:37:11</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -5773,7 +5773,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SD - Cegeka DBMS for Oracle on IaaS [PRD.0.9.002][PV1.0][DV1.0]</t>
+          <t>SD - Cegeka ExaCC Services [PRD.0.4.002][PV1.1][DV1.0]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5788,40 +5788,40 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>59.3</v>
+        <v>61.8</v>
       </c>
       <c r="I96" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>22</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_PROJECT_DESC, TRANSITION_SCOPE</t>
+          <t>ACCEPTANCE_CRITERIA, ASSUMPTIONS_RISKS, CEGEKA_CONTACTS, CHARGING_MECHANISM, CLIENT_RESPONSIBILITIES_2, COMMERCIAL_SHEET, COST_ONE_TIME, COST_RECURRING, OFFER_SECTIONS, OTHER_CONDITIONAL_SOLUTIONS, OTHER_DOCUMENTS, PRESALES_CHECKS, PRESALES_INSTRUCTIONS, QA_CUSTOMERS, ROLES_CEGEKA, ROLES_CUSTOMER, SERVICE_DESCRIPTION_LINK, SKU_INFORMATION, SLA_KPI, TRANSITION_ASSUMPTIONS, TRANSITION_MILESTONES, TRANSITION_SCOPE</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:21</t>
+          <t>2026-03-25 08:37:11</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:24</t>
+          <t>2026-03-25 08:37:15</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
         <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="I97" t="n">
         <v>22</v>
@@ -5872,12 +5872,12 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:17</t>
+          <t>2026-03-25 08:37:42</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-03-24 16:41:21</t>
+          <t>2026-03-25 08:37:46</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -5909,7 +5909,7 @@
         <v>3</v>
       </c>
       <c r="H98" t="n">
-        <v>65.5</v>
+        <v>63.6</v>
       </c>
       <c r="I98" t="n">
         <v>22</v>
@@ -5928,12 +5928,12 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:49</t>
+          <t>2026-03-25 08:40:16</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-03-24 16:43:53</t>
+          <t>2026-03-25 08:40:20</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
